--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122197539</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122197539</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124893197</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>210</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högströmskavägen nordöster, Högströmskavägen nordöster, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471388</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6543795</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>124893197</v>
       </c>
       <c r="B3" t="n">
-        <v>95551</v>
+        <v>95719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -797,11 +797,6 @@
       <c r="B3" t="n">
         <v>95719</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,705 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129489511</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471435</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6543574</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129488615</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96154</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471363</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6543826</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129488723</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92827</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471381</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6543785</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129489398</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471402</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6543654</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födohack på silverlåga.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129490331</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471478</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6543609</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129488280</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96154</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Laxå, Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471378</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6543792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>96158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R4" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>96154</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,43 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R5" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96154</v>
+        <v>96158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,6 +1529,9 @@
           <t>kapslar</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Laxå, Laxå, Nrk</t>
@@ -1583,12 +1586,18 @@
           <t>13:17</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tidigare känd lokal, märkt platsen med gutt märkband.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1604,6 +1613,130 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129503734</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högströmskavägen nordöster, Atlasruta 10E0e (Gåssjön), Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471409</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6543582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hanne kallade och flög runt i området. Har den fångad på film också</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B4" t="n">
-        <v>96158</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,43 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R4" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>96166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,39 +1036,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R5" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96158</v>
+        <v>96166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>96169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R4" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>96166</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,43 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R5" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B4" t="n">
-        <v>96169</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,43 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R4" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>96169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,39 +1036,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R5" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>96169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R4" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>96169</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,43 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R5" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B4" t="n">
-        <v>96169</v>
+        <v>56920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,43 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R4" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>96198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,39 +1036,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R5" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129489398</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>129503734</v>
       </c>
       <c r="B10" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>56920</v>
+        <v>96198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R4" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>56920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,43 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R5" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129489398</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>129503734</v>
       </c>
       <c r="B10" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129489398</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>129503734</v>
       </c>
       <c r="B10" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B4" t="n">
-        <v>96216</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,43 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R4" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B5" t="n">
-        <v>56926</v>
+        <v>96216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,39 +1036,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R5" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>96216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R4" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>96216</v>
+        <v>56926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,43 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R5" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B4" t="n">
-        <v>96220</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,43 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R4" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B5" t="n">
-        <v>56926</v>
+        <v>96222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,39 +1036,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R5" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
         <v>129488723</v>
       </c>
       <c r="B6" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129489511</v>
+        <v>129488615</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>96232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,39 +919,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
+          <t>Laxå, Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471435</v>
+        <v>471363</v>
       </c>
       <c r="R4" t="n">
-        <v>6543574</v>
+        <v>6543826</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bälgrop med fjäder fr tjäderhöna.</t>
+          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129488615</v>
+        <v>129489511</v>
       </c>
       <c r="B5" t="n">
-        <v>96222</v>
+        <v>56926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,43 +1040,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxå, Laxå, Nrk</t>
+          <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471363</v>
+        <v>471435</v>
       </c>
       <c r="R5" t="n">
-        <v>6543826</v>
+        <v>6543574</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tidigare känd lokal. Märkt platsen med gult märkband i gran.</t>
+          <t>Bälgrop med fjäder fr tjäderhöna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1494,7 +1494,7 @@
         <v>129488280</v>
       </c>
       <c r="B9" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,12 +1407,15 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>SV Rankemossen, Stora Rankemossen, Nrk</t>
@@ -1465,6 +1468,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hördes tydligt när andra mesar varnade.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1382,7 +1382,7 @@
         <v>129490331</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,6 +1746,134 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129649435</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högströmskavägen nordöster, Atlasruta 10E0e (Gåssjön), Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>471414</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6543549</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hanne spelar/revirhävdar</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1751,7 +1751,7 @@
         <v>129649435</v>
       </c>
       <c r="B11" t="n">
-        <v>57035</v>
+        <v>57043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1751,7 +1751,7 @@
         <v>129649435</v>
       </c>
       <c r="B11" t="n">
-        <v>57043</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -1627,7 +1627,7 @@
         <v>129503734</v>
       </c>
       <c r="B10" t="n">
-        <v>56917</v>
+        <v>57044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2022 artfynd.xlsx
+++ b/artfynd/A 54302-2022 artfynd.xlsx
@@ -2336,7 +2336,7 @@
         <v>131221427</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
